--- a/results/job_matches_2026-10-16.xlsx
+++ b/results/job_matches_2026-10-16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,52 +596,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI and Data Platform Engineer</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arizona Cardinals</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tempe, AZ, USA USA</t>
+          <t>Sunnyvale, CA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8efb074c3b86d52</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed61fbb4cf30f4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI and Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Curium Pharmaceuticals</t>
+          <t>Arizona Cardinals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Tempe, AZ, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74dcc353cfba7710</t>
+          <t>https://www.indeed.com/viewjob?jk=e8efb074c3b86d52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Curium Pharmaceuticals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nashville, TN, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a8059421c16401</t>
+          <t>https://www.indeed.com/viewjob?jk=74dcc353cfba7710</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PACCAR</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Renton, WA, USA USA</t>
+          <t>Nashville, TN, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,24 +729,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32eca10d6f924cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a8059421c16401</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Data 360)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>PACCAR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Renton, WA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,34 +754,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=144b94b2b27849cf</t>
+          <t>https://www.indeed.com/viewjob?jk=32eca10d6f924cc5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Platform Architect (Data 360)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Georgia Ports Authority</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Savannah, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,42 +789,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e912de19ae209d</t>
+          <t>https://www.indeed.com/viewjob?jk=144b94b2b27849cf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Azenta Life Sciences</t>
+          <t>Georgia Ports Authority</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plainfield, IN, USA USA</t>
+          <t>Savannah, GA, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Medallion Architecture, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd026569b38732b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e912de19ae209d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qualys</t>
+          <t>Azenta Life Sciences</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Plainfield, IN, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Spark, Scala, Kafka, ELT, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Medallion Architecture, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f134635a897a33ef</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd026569b38732b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jobs for you</t>
+          <t>AWS MarTech Developer - Delivery Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rochester, MN, USA USA</t>
+          <t>Mechanicsburg, PA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0635572d7c2a952f</t>
+          <t>https://www.indeed.com/viewjob?jk=0340e7637c307ecd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AWS Application Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durham, NC, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,24 +939,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7548e960636fc13c</t>
+          <t>https://www.indeed.com/viewjob?jk=56720452d0029ef6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS MarTech Developer - Delivery Consultant</t>
+          <t>Jobs for you</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, USA USA</t>
+          <t>Rochester, MN, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,24 +974,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f5106dd1d1fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=0635572d7c2a952f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Application Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Charlottesville, VA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,52 +999,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da230961b3d2ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=cb6e5f849c66e88e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Application Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ALTEN</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, USA USA</t>
+          <t>Durham, NC, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=703d94a82f6814df</t>
+          <t>https://www.indeed.com/viewjob?jk=7548e960636fc13c</t>
         </is>
       </c>
     </row>
@@ -1086,17 +1086,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SRE - DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Symple Lending</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,42 +1104,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, ECS, IAM, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed982ec7d62db1ac</t>
+          <t>https://www.indeed.com/viewjob?jk=eb3df57ec03be7e2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SRE - DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New York City Department of Sanitation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864cc22c0d12e7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ed982ec7d62db1ac</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>State of Oklahoma</t>
+          <t>New York City Department of Sanitation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OK, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316ab24eebea3950</t>
+          <t>https://www.indeed.com/viewjob?jk=864cc22c0d12e7cf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Software and Data Engineer - Software Engineer III- Agentic Pricing</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, NoSQL, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0cd3bb4e3adcf71</t>
+          <t>https://www.indeed.com/viewjob?jk=2b363a6b62d7ea4b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software and Data Engineer - Software Engineer III- Agentic Pricing</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, NoSQL, ELT, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,24 +1254,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b363a6b62d7ea4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0cd3bb4e3adcf71</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CapCenter</t>
+          <t>State of Oklahoma</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, USA USA</t>
+          <t>OK, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1e91f59b7cddbc</t>
+          <t>https://www.indeed.com/viewjob?jk=316ab24eebea3950</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Performance Contracting</t>
+          <t>CapCenter</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lenexa, KS, USA USA</t>
+          <t>Glen Allen, VA, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,17 +1314,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea913bc89d514a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1e91f59b7cddbc</t>
         </is>
       </c>
     </row>
@@ -1359,24 +1359,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b2fdc93de024bc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea913bc89d514a1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. QA Test Engineer (Quality Assurance)</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Performance Contracting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Lenexa, KS, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3932183df2db1bef</t>
+          <t>https://www.indeed.com/viewjob?jk=73b2fdc93de024bc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enterprise GIS Solutions Architect</t>
+          <t>Sr. QA Test Engineer (Quality Assurance)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Symetri</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,32 +1429,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12b11aead05177eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3932183df2db1bef</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise GIS Solutions Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Symetri</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac6d9c5d5ce170c</t>
+          <t>https://www.indeed.com/viewjob?jk=12b11aead05177eb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analyst – Data Products and AI Enablement</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Lake Forest, IL, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, Snowflake, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ad09cd2afe8d04</t>
+          <t>https://www.indeed.com/viewjob?jk=cac6d9c5d5ce170c</t>
         </is>
       </c>
     </row>
@@ -1534,24 +1534,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1121cabf48789bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a1ff9a7450560f5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Analyst – Data Products and AI Enablement</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, Snowflake, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a14e8e38f07dfff</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ad09cd2afe8d04</t>
         </is>
       </c>
     </row>
@@ -1611,17 +1611,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineering - MTS, Trust Intelligence Platform</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Databricks, BigQuery, Spark, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c899c503e1ea64</t>
+          <t>https://www.indeed.com/viewjob?jk=38e8eea54405bd1d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Platform Engineer</t>
+          <t>Software Engineering - MTS, Trust Intelligence Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, BigQuery, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Athena, RDS, Databricks, BigQuery, Spark, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c83099662b4f529b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c899c503e1ea64</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Security Engineer - Network Edge Security</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Azenta Life Sciences</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plainfield, IN, USA USA</t>
+          <t>San Francisco Bay Area, CA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,77 +1699,77 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c8966dca72b6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d42cd7af563ba184</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer - People Analytics</t>
+          <t>Senior Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jackson, MS, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, BigQuery, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ebe194a1359236</t>
+          <t>https://www.indeed.com/viewjob?jk=c83099662b4f529b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BioTouch</t>
+          <t>Azenta Life Sciences</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Midland, GA, USA USA</t>
+          <t>Plainfield, IN, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Snowflake, Dimensional Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07325693acde4343</t>
+          <t>https://www.indeed.com/viewjob?jk=88c8966dca72b6e1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data and AI Engineer</t>
+          <t>Data Engineer - People Analytics</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Montgomery, AL, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,34 +1804,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, NoSQL, Dimensional Modeling, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203bb719c5957421</t>
+          <t>https://www.indeed.com/viewjob?jk=25b838a42e38537c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MORRISON &amp; FOERSTER</t>
+          <t>BioTouch</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Midland, GA, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Snowflake, Dimensional Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990ad175fc5efc37</t>
+          <t>https://www.indeed.com/viewjob?jk=07325693acde4343</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer</t>
+          <t>Senior Data and AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, NoSQL, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,24 +1884,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc48d60affb891da</t>
+          <t>https://www.indeed.com/viewjob?jk=203bb719c5957421</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - People Analytics</t>
+          <t>Senior Azure Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charleston, WV, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,34 +1909,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af5eb4b93d62c15</t>
+          <t>https://www.indeed.com/viewjob?jk=dc48d60affb891da</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track) - Hybrid</t>
+          <t>Senior Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>MORRISON &amp; FOERSTER</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a616499fc546743c</t>
+          <t>https://www.indeed.com/viewjob?jk=990ad175fc5efc37</t>
         </is>
       </c>
     </row>
@@ -1996,17 +1996,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,24 +2024,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee54c8bb60a99024</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa405c41bf04634</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Miami, FL, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa405c41bf04634</t>
+          <t>https://www.indeed.com/viewjob?jk=ee54c8bb60a99024</t>
         </is>
       </c>
     </row>
@@ -2101,17 +2101,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - People Analytics</t>
+          <t>Clinical Data &amp; Reporting Analyst (Data Warehouse Reporting Analyst Sr)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jackson, MS, USA USA</t>
+          <t>Orange, CA, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,17 +2119,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Snowflake, MySQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a742b56a01106583</t>
+          <t>https://www.indeed.com/viewjob?jk=7fcabb0ebbce5f77</t>
         </is>
       </c>
     </row>
@@ -2206,17 +2206,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Clinical Data &amp; Reporting Analyst (Data Warehouse Reporting Analyst Sr)</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Orange, CA, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Snowflake, MySQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,24 +2234,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcabb0ebbce5f77</t>
+          <t>https://www.indeed.com/viewjob?jk=e48935bdabe7b480</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Oracle Database Architect-6</t>
+          <t>Senior BI Platform Operations Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, IAM, RDS, Amazon QuickSight, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,94 +2269,94 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10f6c9f559ca000</t>
+          <t>https://www.indeed.com/viewjob?jk=cce3223e9c173979</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior BI Platform Operations Engineer</t>
+          <t>Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, IAM, RDS, Amazon QuickSight, Tableau</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce3223e9c173979</t>
+          <t>https://www.indeed.com/viewjob?jk=b05d9edb91b34040</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Palantir Application Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48935bdabe7b480</t>
+          <t>https://www.indeed.com/viewjob?jk=3fc1fa95303fa132</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Remote)</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>yasmin@assemblyworksco.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, Azure, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,19 +2374,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05d9edb91b34040</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cb4df5534720f9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Palantir Application Engineer</t>
+          <t>Senior Software Engineer (FIV)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Z&amp;E MANAGEMENT SERVICES CORP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fc1fa95303fa132</t>
+          <t>https://www.indeed.com/viewjob?jk=60dce8a7b936d462</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Data Platform</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Proper Hospitality</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,34 +2434,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9155639e76e6a19f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab782b271a73002</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>yasmin@assemblyworksco.com</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,34 +2469,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cb4df5534720f9</t>
+          <t>https://www.indeed.com/viewjob?jk=4a185408c7e15aee</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (FIV)</t>
+          <t>Senior Solution Engineer - GCC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Z&amp;E MANAGEMENT SERVICES CORP</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,34 +2504,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60dce8a7b936d462</t>
+          <t>https://www.indeed.com/viewjob?jk=151ffa6ede59bb8b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Global Enterprise Applications Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Refresco</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,34 +2539,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab782b271a73002</t>
+          <t>https://www.indeed.com/viewjob?jk=251a5cab33206a0f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer 1 – Full-stack, Generative AI, Cloud</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,24 +2584,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15607638a498d15d</t>
+          <t>https://www.indeed.com/viewjob?jk=190647565eda87d9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Java Full Stack Software Engineer</t>
+          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Malvern, PA, USA USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2618,216 +2618,6 @@
         </is>
       </c>
       <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6899e4e4be880d8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Irving, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a185408c7e15aee</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Senior Solution Engineer - GCC</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, USA USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=151ffa6ede59bb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Global Enterprise Applications Developer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Refresco</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Tampa, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=251a5cab33206a0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Advanced AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, USA USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Vertex AI, Scala, PostgreSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=878b0744411a1f9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=190647565eda87d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Siemens Healthineers</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Malvern, PA, USA USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e0290081386678f8</t>
         </is>

--- a/results/job_matches_2026-10-16.xlsx
+++ b/results/job_matches_2026-10-16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,17 +526,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>Culligan Water</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Rosemont, IL, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Dataflow, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,77 +554,77 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85753248df0ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=8647c65f36c20d2b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Culligan Water</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rosemont, IL, USA USA</t>
+          <t>Sunnyvale, CA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Dataflow, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8647c65f36c20d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed61fbb4cf30f4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Curium Pharmaceuticals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed61fbb4cf30f4</t>
+          <t>https://www.indeed.com/viewjob?jk=74dcc353cfba7710</t>
         </is>
       </c>
     </row>
@@ -666,25 +666,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Curium Pharmaceuticals</t>
+          <t>PACCAR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Renton, WA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Spark, PySpark</t>
+          <t>IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74dcc353cfba7710</t>
+          <t>https://www.indeed.com/viewjob?jk=32eca10d6f924cc5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Platform Architect (Data 360)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nashville, TN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,34 +719,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a8059421c16401</t>
+          <t>https://www.indeed.com/viewjob?jk=144b94b2b27849cf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PACCAR</t>
+          <t>Georgia Ports Authority</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Renton, WA, USA USA</t>
+          <t>Savannah, GA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,102 +764,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32eca10d6f924cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e912de19ae209d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Data 360)</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Azenta Life Sciences</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Plainfield, IN, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Medallion Architecture, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=144b94b2b27849cf</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd026569b38732b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Database Engineer Detroit</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Georgia Ports Authority</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Savannah, GA, USA USA</t>
+          <t>Detroit, MI, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e912de19ae209d</t>
+          <t>https://www.indeed.com/viewjob?jk=21edb2bdecbf61b1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Azenta Life Sciences</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plainfield, IN, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Medallion Architecture, Scala, Snowflake, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd026569b38732b</t>
+          <t>https://www.indeed.com/viewjob?jk=1da230961b3d2ebf</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, USA USA</t>
+          <t>Lake Mary, FL, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0340e7637c307ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=35f5106dd1d1fe70</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56720452d0029ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=832f3f53a36aa70e</t>
         </is>
       </c>
     </row>
@@ -1016,17 +1016,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AWS Application Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>OakBase Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Durham, NC, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7548e960636fc13c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d89c18decc68ed9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Clear Capital</t>
+          <t>Symple Lending</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Reno, NV, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, ECS, IAM, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9401910d281a0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb3df57ec03be7e2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Symple Lending</t>
+          <t>Clear Capital</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Reno, NV, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, ECS, IAM, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb3df57ec03be7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c9401910d281a0d3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SRE - DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>New York City Department of Sanitation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed982ec7d62db1ac</t>
+          <t>https://www.indeed.com/viewjob?jk=864cc22c0d12e7cf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New York City Department of Sanitation</t>
+          <t>State of Oklahoma</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>OK, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864cc22c0d12e7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=316ab24eebea3950</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software and Data Engineer - Software Engineer III- Agentic Pricing</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CapCenter</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Glen Allen, VA, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,34 +1209,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, NoSQL, ELT, Splunk, CI/CD</t>
+          <t>RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b363a6b62d7ea4b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1e91f59b7cddbc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Performance Contracting</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Lenexa, KS, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,24 +1254,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0cd3bb4e3adcf71</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea913bc89d514a1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>State of Oklahoma</t>
+          <t>Performance Contracting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OK, USA USA</t>
+          <t>Lenexa, KS, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316ab24eebea3950</t>
+          <t>https://www.indeed.com/viewjob?jk=73b2fdc93de024bc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Sr. QA Test Engineer (Quality Assurance)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CapCenter</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,34 +1314,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1e91f59b7cddbc</t>
+          <t>https://www.indeed.com/viewjob?jk=3932183df2db1bef</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Enterprise GIS Solutions Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Performance Contracting</t>
+          <t>Symetri</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lenexa, KS, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea913bc89d514a1</t>
+          <t>https://www.indeed.com/viewjob?jk=12b11aead05177eb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Performance Contracting</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lenexa, KS, USA USA</t>
+          <t>Lake Forest, IL, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,32 +1394,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b2fdc93de024bc</t>
+          <t>https://www.indeed.com/viewjob?jk=cac6d9c5d5ce170c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. QA Test Engineer (Quality Assurance)</t>
+          <t>Data &amp; AI Engineer, Advanced</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Naval Nuclear Laboratory</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Niskayuna, NY, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,32 +1429,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3932183df2db1bef</t>
+          <t>https://www.indeed.com/viewjob?jk=1121cabf48789bf1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enterprise GIS Solutions Architect</t>
+          <t>Analyst – Data Products and AI Enablement</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Symetri</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, Snowflake, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12b11aead05177eb</t>
+          <t>https://www.indeed.com/viewjob?jk=52c49e28c5180f66</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Elyon International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac6d9c5d5ce170c</t>
+          <t>https://www.indeed.com/viewjob?jk=507c4a778f7f2110</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer, Advanced</t>
+          <t>Analyst – Data Products and AI Enablement</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Naval Nuclear Laboratory</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Niskayuna, NY, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, Snowflake, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,24 +1534,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a1ff9a7450560f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ad09cd2afe8d04</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analyst – Data Products and AI Enablement</t>
+          <t>IT-Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Clifton Park, NY, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, Snowflake, CI/CD, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ad09cd2afe8d04</t>
+          <t>https://www.indeed.com/viewjob?jk=aca652d2e35ef7a6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineering - MTS, Trust Intelligence Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Elyon International</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,34 +1594,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Athena, RDS, Databricks, BigQuery, Spark, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507c4a778f7f2110</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c899c503e1ea64</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Security Engineer - Network Edge Security</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>San Francisco Bay Area, CA, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e8eea54405bd1d</t>
+          <t>https://www.indeed.com/viewjob?jk=d42cd7af563ba184</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineering - MTS, Trust Intelligence Platform</t>
+          <t>Senior Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Databricks, BigQuery, Spark, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, BigQuery, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c899c503e1ea64</t>
+          <t>https://www.indeed.com/viewjob?jk=c83099662b4f529b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Security Engineer - Network Edge Security</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42cd7af563ba184</t>
+          <t>https://www.indeed.com/viewjob?jk=38e8eea54405bd1d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>Azenta Life Sciences</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Plainfield, IN, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, BigQuery, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,59 +1744,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c83099662b4f529b</t>
+          <t>https://www.indeed.com/viewjob?jk=88c8966dca72b6e1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - People Analytics</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Azenta Life Sciences</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plainfield, IN, USA USA</t>
+          <t>Montgomery, AL, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c8966dca72b6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2a34d2988258872a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - People Analytics</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BioTouch</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montgomery, AL, USA USA</t>
+          <t>Midland, GA, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,34 +1804,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Snowflake, Dimensional Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b838a42e38537c</t>
+          <t>https://www.indeed.com/viewjob?jk=07325693acde4343</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Azure Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BioTouch</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Midland, GA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Snowflake, Dimensional Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07325693acde4343</t>
+          <t>https://www.indeed.com/viewjob?jk=dc48d60affb891da</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data and AI Engineer</t>
+          <t>Data Engineer - People Analytics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Montgomery, AL, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,34 +1874,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, NoSQL, Dimensional Modeling, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203bb719c5957421</t>
+          <t>https://www.indeed.com/viewjob?jk=25b838a42e38537c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer</t>
+          <t>Enterprise Account Executive (Telco)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,34 +1909,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc48d60affb891da</t>
+          <t>https://www.indeed.com/viewjob?jk=65e1984b6c60dff9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MORRISON &amp; FOERSTER</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Miami, FL, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Azure Monitor</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990ad175fc5efc37</t>
+          <t>https://www.indeed.com/viewjob?jk=ee54c8bb60a99024</t>
         </is>
       </c>
     </row>
@@ -2031,17 +2031,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Part time Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>GeoVisual Analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, YARN, NoSQL, dbt, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee54c8bb60a99024</t>
+          <t>https://www.indeed.com/viewjob?jk=e946bc71de41def8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Part time Sr. Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GeoVisual Analytics</t>
+          <t>Children's Healthcare of Atlanta</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Brookhaven, GA, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, YARN, NoSQL, dbt, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e946bc71de41def8</t>
+          <t>https://www.indeed.com/viewjob?jk=2dab3ac5d3446af2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Clinical Data &amp; Reporting Analyst (Data Warehouse Reporting Analyst Sr)</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Orange, CA, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Snowflake, MySQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcabb0ebbce5f77</t>
+          <t>https://www.indeed.com/viewjob?jk=98106ef012e89694</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer - People Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Children's Healthcare of Atlanta</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brookhaven, GA, USA USA</t>
+          <t>Jackson, MS, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,34 +2154,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dab3ac5d3446af2</t>
+          <t>https://www.indeed.com/viewjob?jk=a742b56a01106583</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,94 +2199,94 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98106ef012e89694</t>
+          <t>https://www.indeed.com/viewjob?jk=e48935bdabe7b480</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48935bdabe7b480</t>
+          <t>https://www.indeed.com/viewjob?jk=b05d9edb91b34040</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior BI Platform Operations Engineer</t>
+          <t>Palantir Application Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, IAM, RDS, Amazon QuickSight, Tableau</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce3223e9c173979</t>
+          <t>https://www.indeed.com/viewjob?jk=3fc1fa95303fa132</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Remote)</t>
+          <t>Senior Software Engineer (FIV)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Z&amp;E MANAGEMENT SERVICES CORP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,24 +2304,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05d9edb91b34040</t>
+          <t>https://www.indeed.com/viewjob?jk=60dce8a7b936d462</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Palantir Application Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,24 +2339,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fc1fa95303fa132</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab782b271a73002</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>yasmin@assemblyworksco.com</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,34 +2364,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cb4df5534720f9</t>
+          <t>https://www.indeed.com/viewjob?jk=4a185408c7e15aee</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (FIV)</t>
+          <t>Senior Solution Engineer - GCC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Z&amp;E MANAGEMENT SERVICES CORP</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,34 +2399,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60dce8a7b936d462</t>
+          <t>https://www.indeed.com/viewjob?jk=151ffa6ede59bb8b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Global Enterprise Applications Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Refresco</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,34 +2434,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab782b271a73002</t>
+          <t>https://www.indeed.com/viewjob?jk=251a5cab33206a0f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, CI/CD, Docker</t>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a185408c7e15aee</t>
+          <t>https://www.indeed.com/viewjob?jk=190647565eda87d9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Solution Engineer - GCC</t>
+          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, USA USA</t>
+          <t>Malvern, PA, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2513,111 +2513,6 @@
         </is>
       </c>
       <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=151ffa6ede59bb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Global Enterprise Applications Developer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Refresco</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Tampa, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=251a5cab33206a0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=190647565eda87d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Siemens Healthineers</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Malvern, PA, USA USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e0290081386678f8</t>
         </is>

--- a/results/job_matches_2026-10-16.xlsx
+++ b/results/job_matches_2026-10-16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,12 +566,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,59 +589,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed61fbb4cf30f4</t>
+          <t>https://www.indeed.com/viewjob?jk=618da1fd3349a9e4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Curium Pharmaceuticals</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Sunnyvale, CA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74dcc353cfba7710</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed61fbb4cf30f4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI and Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arizona Cardinals</t>
+          <t>Curium Pharmaceuticals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tempe, AZ, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8efb074c3b86d52</t>
+          <t>https://www.indeed.com/viewjob?jk=74dcc353cfba7710</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI and Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PACCAR</t>
+          <t>Arizona Cardinals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Renton, WA, USA USA</t>
+          <t>Tempe, AZ, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32eca10d6f924cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8efb074c3b86d52</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Data 360)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>PACCAR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Renton, WA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,34 +719,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=144b94b2b27849cf</t>
+          <t>https://www.indeed.com/viewjob?jk=32eca10d6f924cc5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Platform Architect (Data 360)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Georgia Ports Authority</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Savannah, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,42 +754,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e912de19ae209d</t>
+          <t>https://www.indeed.com/viewjob?jk=144b94b2b27849cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Azenta Life Sciences</t>
+          <t>Georgia Ports Authority</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plainfield, IN, USA USA</t>
+          <t>Savannah, GA, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Medallion Architecture, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,24 +799,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd026569b38732b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e912de19ae209d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Database Engineer Detroit</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>New Hampshire Mutual Bancorp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Detroit, MI, USA USA</t>
+          <t>Concord, NH, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21edb2bdecbf61b1</t>
+          <t>https://www.indeed.com/viewjob?jk=013237d4696c82bd</t>
         </is>
       </c>
     </row>
@@ -846,55 +846,55 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Edison, NJ, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da230961b3d2ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=257cf3b26e3ac665</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS MarTech Developer - Delivery Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, USA USA</t>
+          <t>Dania Beach, FL, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,67 +904,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f5106dd1d1fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=efe5f6ebca22f7eb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform Engineer I</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Azenta Life Sciences</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Plainfield, IN, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Medallion Architecture, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832f3f53a36aa70e</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd026569b38732b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jobs for you</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rochester, MN, USA USA</t>
+          <t>Miami, FL, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0635572d7c2a952f</t>
+          <t>https://www.indeed.com/viewjob?jk=a3abc7d40fac1d76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AWS Application Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, USA USA</t>
+          <t>Cincinnati, OH, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,42 +1009,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb6e5f849c66e88e</t>
+          <t>https://www.indeed.com/viewjob?jk=71b643cc943fe0db</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OakBase Technologies</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Antonio, TX, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d89c18decc68ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
         </is>
       </c>
     </row>
@@ -1056,20 +1056,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Symple Lending</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Erlanger, KY, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, ECS, IAM, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb3df57ec03be7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0631f7e796ccb99</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Clear Capital</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reno, NV, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, ELT, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,102 +1114,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9401910d281a0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=56720452d0029ef6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS MarTech Developer - Delivery Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New York City Department of Sanitation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864cc22c0d12e7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=96725a6630248399</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Platform Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>State of Oklahoma</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OK, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316ab24eebea3950</t>
+          <t>https://www.indeed.com/viewjob?jk=832f3f53a36aa70e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Jobs for you</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CapCenter</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, USA USA</t>
+          <t>Rochester, MN, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,67 +1219,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1e91f59b7cddbc</t>
+          <t>https://www.indeed.com/viewjob?jk=0635572d7c2a952f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior AWS Application Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Performance Contracting</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lenexa, KS, USA USA</t>
+          <t>Durham, NC, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea913bc89d514a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7548e960636fc13c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Performance Contracting</t>
+          <t>OakBase Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lenexa, KS, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,102 +1289,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b2fdc93de024bc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d89c18decc68ed9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. QA Test Engineer (Quality Assurance)</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Clear Capital</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Reno, NV, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3932183df2db1bef</t>
+          <t>https://www.indeed.com/viewjob?jk=c9401910d281a0d3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Enterprise GIS Solutions Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Symetri</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12b11aead05177eb</t>
+          <t>https://www.indeed.com/viewjob?jk=36cc4c2d066dc5e3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>State of Oklahoma</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, USA USA</t>
+          <t>OK, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,67 +1394,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac6d9c5d5ce170c</t>
+          <t>https://www.indeed.com/viewjob?jk=316ab24eebea3950</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer, Advanced</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Naval Nuclear Laboratory</t>
+          <t>CapCenter</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Niskayuna, NY, USA USA</t>
+          <t>Glen Allen, VA, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1121cabf48789bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1e91f59b7cddbc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Analyst – Data Products and AI Enablement</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Performance Contracting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Lenexa, KS, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, Snowflake, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,32 +1464,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52c49e28c5180f66</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea913bc89d514a1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Elyon International</t>
+          <t>Performance Contracting</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Lenexa, KS, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,32 +1499,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507c4a778f7f2110</t>
+          <t>https://www.indeed.com/viewjob?jk=73b2fdc93de024bc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analyst – Data Products and AI Enablement</t>
+          <t>Sr. QA Test Engineer (Quality Assurance)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, Snowflake, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,24 +1534,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ad09cd2afe8d04</t>
+          <t>https://www.indeed.com/viewjob?jk=3932183df2db1bef</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IT-Engineer</t>
+          <t>Data &amp; AI Engineer, Advanced</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Naval Nuclear Laboratory</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Clifton Park, NY, USA USA</t>
+          <t>Niskayuna, NY, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,29 +1559,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca652d2e35ef7a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1121cabf48789bf1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineering - MTS, Trust Intelligence Platform</t>
+          <t>Analyst – Data Products and AI Enablement</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1594,34 +1594,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Databricks, BigQuery, Spark, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, Snowflake, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c899c503e1ea64</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ad09cd2afe8d04</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Security Engineer - Network Edge Security</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Elyon International</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,34 +1629,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42cd7af563ba184</t>
+          <t>https://www.indeed.com/viewjob?jk=507c4a778f7f2110</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Platform Engineer</t>
+          <t>Mid-Level Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>Academian</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, BigQuery, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c83099662b4f529b</t>
+          <t>https://www.indeed.com/viewjob?jk=6f47628601624696</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>IT-Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Clifton Park, NY, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e8eea54405bd1d</t>
+          <t>https://www.indeed.com/viewjob?jk=aca652d2e35ef7a6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering - MTS, Trust Intelligence Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Azenta Life Sciences</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plainfield, IN, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,42 +1734,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Athena, RDS, Databricks, BigQuery, Spark, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c8966dca72b6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c899c503e1ea64</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer - People Analytics</t>
+          <t>Security Engineer - Network Edge Security</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montgomery, AL, USA USA</t>
+          <t>San Francisco Bay Area, CA, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,32 +1779,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a34d2988258872a</t>
+          <t>https://www.indeed.com/viewjob?jk=d42cd7af563ba184</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BioTouch</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Midland, GA, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Snowflake, Dimensional Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, BigQuery, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,94 +1814,94 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07325693acde4343</t>
+          <t>https://www.indeed.com/viewjob?jk=c83099662b4f529b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc48d60affb891da</t>
+          <t>https://www.indeed.com/viewjob?jk=38e8eea54405bd1d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - People Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Azenta Life Sciences</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Montgomery, AL, USA USA</t>
+          <t>Plainfield, IN, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b838a42e38537c</t>
+          <t>https://www.indeed.com/viewjob?jk=88c8966dca72b6e1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Enterprise Account Executive (Telco)</t>
+          <t>Data Engineer - People Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bellevue, WA, USA USA</t>
+          <t>Montgomery, AL, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,24 +1919,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65e1984b6c60dff9</t>
+          <t>https://www.indeed.com/viewjob?jk=25b838a42e38537c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,34 +1944,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee54c8bb60a99024</t>
+          <t>https://www.indeed.com/viewjob?jk=a13eef95390e13e6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Customer Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LakeFusion</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,34 +1979,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
+          <t>Redshift, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685fcc351210ac8f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>BioTouch</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Midland, GA, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Snowflake, Dimensional Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,24 +2024,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa405c41bf04634</t>
+          <t>https://www.indeed.com/viewjob?jk=07325693acde4343</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Part time Sr. Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GeoVisual Analytics</t>
+          <t>Fandom</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Virginia Beach, VA, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,34 +2049,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, YARN, NoSQL, dbt, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e946bc71de41def8</t>
+          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer - People Analytics</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Children's Healthcare of Atlanta</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brookhaven, GA, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,34 +2084,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dab3ac5d3446af2</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfa2bfed453e06d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Data Engineer - People Analytics</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Columbia, SC, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,34 +2119,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98106ef012e89694</t>
+          <t>https://www.indeed.com/viewjob?jk=ed27dc46592226d5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - People Analytics</t>
+          <t>Enterprise Account Executive (Telco)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jackson, MS, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a742b56a01106583</t>
+          <t>https://www.indeed.com/viewjob?jk=65e1984b6c60dff9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LakeFusion</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,172 +2199,172 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48935bdabe7b480</t>
+          <t>https://www.indeed.com/viewjob?jk=685fcc351210ac8f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Remote)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Miami, FL, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05d9edb91b34040</t>
+          <t>https://www.indeed.com/viewjob?jk=ee54c8bb60a99024</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Palantir Application Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fc1fa95303fa132</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa405c41bf04634</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (FIV)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Z&amp;E MANAGEMENT SERVICES CORP</t>
+          <t>Children's Healthcare of Atlanta</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Brookhaven, GA, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60dce8a7b936d462</t>
+          <t>https://www.indeed.com/viewjob?jk=2dab3ac5d3446af2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab782b271a73002</t>
+          <t>https://www.indeed.com/viewjob?jk=98106ef012e89694</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a185408c7e15aee</t>
+          <t>https://www.indeed.com/viewjob?jk=e48935bdabe7b480</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Solution Engineer - GCC</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bellevue, WA, USA USA</t>
+          <t>Research Triangle Park, NC, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,34 +2399,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151ffa6ede59bb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=f0942610ce440498</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Global Enterprise Applications Developer</t>
+          <t>Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Refresco</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,29 +2434,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251a5cab33206a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=b05d9edb91b34040</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>DBT / Analytical Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>InApp</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2469,34 +2469,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>Snowflake, Oracle, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, Fact Tables, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=190647565eda87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7b553b68d58c93</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
+          <t>Palantir Application Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Malvern, PA, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,17 +2504,262 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fc1fa95303fa132</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (FIV)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Z&amp;E MANAGEMENT SERVICES CORP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Houston, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Power BI, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60dce8a7b936d462</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ab782b271a73002</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Solution Engineer - GCC</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, USA USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=151ffa6ede59bb8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Global Enterprise Applications Developer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Refresco</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Tampa, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=251a5cab33206a0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=190647565eda87d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Siemens Healthineers</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Malvern, PA, USA USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e0290081386678f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Automation &amp; Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KPIT Technologies</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34953ee9e43bedae</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-16.xlsx
+++ b/results/job_matches_2026-10-16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jobs for you</t>
+          <t>Senior Database Engineer / Data Platform Engineer - Contract</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Techniche Software Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rochester, MN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -474,7 +474,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,112 +484,112 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c0ce292aee499f</t>
+          <t>https://www.indeed.com/viewjob?jk=c608dc1a7f91a8fd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer</t>
+          <t>Jobs for you</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Rochester, MN, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Cloud Storage</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422d054892229b68</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c0ce292aee499f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Culligan Water</t>
+          <t>Lowenstein Sandler</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rosemont, IL, USA USA</t>
+          <t>Roseland, NJ, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Dataflow, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8647c65f36c20d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a132c337eb72501b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Consultant, Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Cloud Storage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618da1fd3349a9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=422d054892229b68</t>
         </is>
       </c>
     </row>
@@ -601,12 +601,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,94 +624,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed61fbb4cf30f4</t>
+          <t>https://www.indeed.com/viewjob?jk=618da1fd3349a9e4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Curium Pharmaceuticals</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Sunnyvale, CA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74dcc353cfba7710</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed61fbb4cf30f4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI and Data Platform Engineer</t>
+          <t>Data Platform Architect (Data 360)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arizona Cardinals</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tempe, AZ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8efb074c3b86d52</t>
+          <t>https://www.indeed.com/viewjob?jk=144b94b2b27849cf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AID&amp;E - AI Governance &amp; Responsible AI - Senior - Consulting</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PACCAR</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Renton, WA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,34 +719,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Vertex AI, Scala, Oracle, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32eca10d6f924cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=7623ac8c1f35092b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Data 360)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,24 +764,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=144b94b2b27849cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3da49be1f8af5184</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Georgia Ports Authority</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Savannah, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,17 +789,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e912de19ae209d</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1b0e4f8d04d392</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dania Beach, FL, USA USA</t>
+          <t>Cincinnati, OH, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe5f6ebca22f7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=71b643cc943fe0db</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Azenta Life Sciences</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plainfield, IN, USA USA</t>
+          <t>Erlanger, KY, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,34 +929,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Medallion Architecture, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd026569b38732b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0631f7e796ccb99</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,24 +974,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3abc7d40fac1d76</t>
+          <t>https://www.indeed.com/viewjob?jk=342dda267d31c163</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b643cc943fe0db</t>
+          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,32 +1044,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
+          <t>https://www.indeed.com/viewjob?jk=56720452d0029ef6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Application Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Erlanger, KY, USA USA</t>
+          <t>Ontario, CA, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0631f7e796ccb99</t>
+          <t>https://www.indeed.com/viewjob?jk=a9769a64429bfdf0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56720452d0029ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=832f3f53a36aa70e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS MarTech Developer - Delivery Consultant</t>
+          <t>Jobs for you</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>Rochester, MN, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96725a6630248399</t>
+          <t>https://www.indeed.com/viewjob?jk=0635572d7c2a952f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Engineer I</t>
+          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832f3f53a36aa70e</t>
+          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jobs for you</t>
+          <t>AWS MarTech Developer - Delivery Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rochester, MN, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0635572d7c2a952f</t>
+          <t>https://www.indeed.com/viewjob?jk=96725a6630248399</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AWS Application Engineer</t>
+          <t>AWS MarTech Developer - Delivery Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,24 +1254,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7548e960636fc13c</t>
+          <t>https://www.indeed.com/viewjob?jk=04f878d842549645</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OakBase Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Antonio, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,17 +1279,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d89c18decc68ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=c54fb94ffc70f02c</t>
         </is>
       </c>
     </row>
@@ -1436,122 +1436,122 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Data Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Performance Contracting</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lenexa, KS, USA USA</t>
+          <t>Omaha, NE, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Databricks Lakehouse, SQL Server, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea913bc89d514a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e10df7e2a6a34c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Performance Contracting</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lenexa, KS, USA USA</t>
+          <t>IL, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b2fdc93de024bc</t>
+          <t>https://www.indeed.com/viewjob?jk=f64ebc7fe9e07abe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. QA Test Engineer (Quality Assurance)</t>
+          <t>Mid-Level Full Stack Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Academian</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3932183df2db1bef</t>
+          <t>https://www.indeed.com/viewjob?jk=6f47628601624696</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer, Advanced</t>
+          <t>IT-Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Naval Nuclear Laboratory</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Niskayuna, NY, USA USA</t>
+          <t>Clifton Park, NY, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,29 +1559,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, RDS, Azure, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1121cabf48789bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=aca652d2e35ef7a6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analyst – Data Products and AI Enablement</t>
+          <t>Software Engineering - MTS, Trust Intelligence Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1594,34 +1594,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, Snowflake, CI/CD, Docker</t>
+          <t>AWS, Athena, RDS, Databricks, BigQuery, Spark, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ad09cd2afe8d04</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c899c503e1ea64</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Security Engineer - Network Edge Security</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Elyon International</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>San Francisco Bay Area, CA, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,34 +1629,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507c4a778f7f2110</t>
+          <t>https://www.indeed.com/viewjob?jk=d42cd7af563ba184</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mid-Level Full Stack Developer</t>
+          <t>Senior Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Academian</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, BigQuery, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f47628601624696</t>
+          <t>https://www.indeed.com/viewjob?jk=c83099662b4f529b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IT-Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Clifton Park, NY, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,32 +1709,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca652d2e35ef7a6</t>
+          <t>https://www.indeed.com/viewjob?jk=38e8eea54405bd1d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineering - MTS, Trust Intelligence Platform</t>
+          <t>Data Engineer - People Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Montgomery, AL, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Databricks, BigQuery, Spark, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,32 +1744,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c899c503e1ea64</t>
+          <t>https://www.indeed.com/viewjob?jk=25b838a42e38537c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Security Engineer - Network Edge Security</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,67 +1779,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42cd7af563ba184</t>
+          <t>https://www.indeed.com/viewjob?jk=a13eef95390e13e6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Platform Engineer</t>
+          <t>Customer Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, BigQuery, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c83099662b4f529b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Fandom</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Virginia Beach, VA, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,59 +1849,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e8eea54405bd1d</t>
+          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Account Executive (Telco)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Azenta Life Sciences</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plainfield, IN, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c8966dca72b6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=65e1984b6c60dff9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - People Analytics</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LakeFusion</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Montgomery, AL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,24 +1919,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b838a42e38537c</t>
+          <t>https://www.indeed.com/viewjob?jk=71bf44c1b8f903d7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Miami, FL, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,34 +1944,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13eef95390e13e6</t>
+          <t>https://www.indeed.com/viewjob?jk=ee54c8bb60a99024</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Customer Engineer, Data &amp; Analytics</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Premier Cloud</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,34 +1979,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa405c41bf04634</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BioTouch</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Midland, GA, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Snowflake, Dimensional Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,24 +2024,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07325693acde4343</t>
+          <t>https://www.indeed.com/viewjob?jk=98106ef012e89694</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,42 +2049,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
+          <t>https://www.indeed.com/viewjob?jk=e48935bdabe7b480</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - People Analytics</t>
+          <t>Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,32 +2094,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfa2bfed453e06d</t>
+          <t>https://www.indeed.com/viewjob?jk=b05d9edb91b34040</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - People Analytics</t>
+          <t>DBT / Analytical Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>InApp</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbia, SC, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
+          <t>Snowflake, Oracle, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, Fact Tables, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,32 +2129,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed27dc46592226d5</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7b553b68d58c93</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Enterprise Account Executive (Telco)</t>
+          <t>Palantir Application Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bellevue, WA, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,102 +2164,102 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65e1984b6c60dff9</t>
+          <t>https://www.indeed.com/viewjob?jk=3fc1fa95303fa132</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Software Engineer (FIV)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LakeFusion</t>
+          <t>Z&amp;E MANAGEMENT SERVICES CORP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685fcc351210ac8f</t>
+          <t>https://www.indeed.com/viewjob?jk=60dce8a7b936d462</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee54c8bb60a99024</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab782b271a73002</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Solution Engineer - GCC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,32 +2269,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa405c41bf04634</t>
+          <t>https://www.indeed.com/viewjob?jk=151ffa6ede59bb8b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Children's Healthcare of Atlanta</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brookhaven, GA, USA USA</t>
+          <t>Malvern, PA, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,32 +2304,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dab3ac5d3446af2</t>
+          <t>https://www.indeed.com/viewjob?jk=e0290081386678f8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Global Enterprise Applications Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Refresco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,425 +2339,40 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98106ef012e89694</t>
+          <t>https://www.indeed.com/viewjob?jk=251a5cab33206a0f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e48935bdabe7b480</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, USA USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0942610ce440498</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Dallas, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b05d9edb91b34040</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>DBT / Analytical Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>InApp</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Snowflake, Oracle, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, Fact Tables, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7b553b68d58c93</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Palantir Application Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Houston, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fc1fa95303fa132</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (FIV)</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Z&amp;E MANAGEMENT SERVICES CORP</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Houston, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Power BI, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60dce8a7b936d462</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab782b271a73002</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Senior Solution Engineer - GCC</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, USA USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=151ffa6ede59bb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Global Enterprise Applications Developer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Refresco</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Tampa, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=251a5cab33206a0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=190647565eda87d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Siemens Healthineers</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Malvern, PA, USA USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0290081386678f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Automation &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>KPIT Technologies</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=34953ee9e43bedae</t>
         </is>

--- a/results/job_matches_2026-10-16.xlsx
+++ b/results/job_matches_2026-10-16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Database Engineer / Data Platform Engineer - Contract</t>
+          <t>Senior Data Engineer - API Platform Engineer - CDH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Techniche Software Solutions</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Rochester, MN, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -474,7 +474,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,24 +484,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c608dc1a7f91a8fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c0ce292aee499f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jobs for you</t>
+          <t>Senior Database Engineer / Data Platform Engineer - Contract</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Techniche Software Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rochester, MN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c0ce292aee499f</t>
+          <t>https://www.indeed.com/viewjob?jk=c608dc1a7f91a8fd</t>
         </is>
       </c>
     </row>
@@ -601,12 +601,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Sunnyvale, CA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618da1fd3349a9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed61fbb4cf30f4</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed61fbb4cf30f4</t>
+          <t>https://www.indeed.com/viewjob?jk=618da1fd3349a9e4</t>
         </is>
       </c>
     </row>
@@ -736,17 +736,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Antonio, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,24 +764,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da49be1f8af5184</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1b0e4f8d04d392</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1b0e4f8d04d392</t>
+          <t>https://www.indeed.com/viewjob?jk=3da49be1f8af5184</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New Hampshire Mutual Bancorp</t>
+          <t>Prolaio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Concord, NH, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013237d4696c82bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e6c438a9913e4f</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>New Hampshire Mutual Bancorp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, USA USA</t>
+          <t>Concord, NH, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b643cc943fe0db</t>
+          <t>https://www.indeed.com/viewjob?jk=013237d4696c82bd</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342dda267d31c163</t>
+          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
+          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS MarTech Developer - Delivery Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56720452d0029ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=96725a6630248399</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AWS Application Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ontario, CA, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9769a64429bfdf0</t>
+          <t>https://www.indeed.com/viewjob?jk=56720452d0029ef6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Platform Engineer I</t>
+          <t>Data Engineer - API Platform Engineer - CDH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Rochester, MN, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832f3f53a36aa70e</t>
+          <t>https://www.indeed.com/viewjob?jk=0635572d7c2a952f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jobs for you</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rochester, MN, USA USA</t>
+          <t>Highlands Ranch, CO, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0635572d7c2a952f</t>
+          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
+          <t>Solution Architect, AI &amp; Cloud</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Advantage Investigations</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sunrise, FL, USA USA</t>
+          <t>Thomasville, NC, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
+          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96725a6630248399</t>
+          <t>https://www.indeed.com/viewjob?jk=04f878d842549645</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS MarTech Developer - Delivery Consultant</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,32 +1254,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f878d842549645</t>
+          <t>https://www.indeed.com/viewjob?jk=c54fb94ffc70f02c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Clear Capital</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Reno, NV, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54fb94ffc70f02c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9401910d281a0d3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Clear Capital</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reno, NV, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,32 +1324,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9401910d281a0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36cc4c2d066dc5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
         </is>
       </c>
     </row>
@@ -1646,17 +1646,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Platform Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, BigQuery, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c83099662b4f529b</t>
+          <t>https://www.indeed.com/viewjob?jk=38e8eea54405bd1d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Solution Engineer (Expansion)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Menlo Park, CA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,32 +1709,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e8eea54405bd1d</t>
+          <t>https://www.indeed.com/viewjob?jk=02e9257f6a31076a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer - People Analytics</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Patterson Companies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Montgomery, AL, USA USA</t>
+          <t>CA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,24 +1744,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b838a42e38537c</t>
+          <t>https://www.indeed.com/viewjob?jk=52f903c2e0d09915</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - People Analytics</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Montgomery, AL, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13eef95390e13e6</t>
+          <t>https://www.indeed.com/viewjob?jk=25b838a42e38537c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Customer Engineer, Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Premier Cloud</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,24 +1814,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a13eef95390e13e6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Customer Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Redshift, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
+          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enterprise Account Executive (Telco)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Fandom</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bellevue, WA, USA USA</t>
+          <t>Virginia Beach, VA, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65e1984b6c60dff9</t>
+          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
         </is>
       </c>
     </row>
@@ -1926,17 +1926,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Enterprise Account Executive (Telco)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,34 +1944,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee54c8bb60a99024</t>
+          <t>https://www.indeed.com/viewjob?jk=65e1984b6c60dff9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Amalgamated Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,17 +1979,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa405c41bf04634</t>
+          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
         </is>
       </c>
     </row>
@@ -2031,52 +2031,52 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48935bdabe7b480</t>
+          <t>https://www.indeed.com/viewjob?jk=b05d9edb91b34040</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Remote)</t>
+          <t>DBT / Analytical Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>InApp</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Snowflake, Oracle, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, Fact Tables, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05d9edb91b34040</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7b553b68d58c93</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DBT / Analytical Engineer</t>
+          <t>Palantir Application Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>InApp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Snowflake, Oracle, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, Fact Tables, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,19 +2129,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7b553b68d58c93</t>
+          <t>https://www.indeed.com/viewjob?jk=3fc1fa95303fa132</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Palantir Application Engineer</t>
+          <t>Senior Software Engineer (FIV)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Z&amp;E MANAGEMENT SERVICES CORP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fc1fa95303fa132</t>
+          <t>https://www.indeed.com/viewjob?jk=60dce8a7b936d462</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (FIV)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Z&amp;E MANAGEMENT SERVICES CORP</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,24 +2199,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60dce8a7b936d462</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab782b271a73002</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2233,146 +2233,6 @@
         </is>
       </c>
       <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab782b271a73002</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior Solution Engineer - GCC</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, USA USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=151ffa6ede59bb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Siemens Healthineers</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Malvern, PA, USA USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0290081386678f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Global Enterprise Applications Developer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Refresco</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Tampa, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=251a5cab33206a0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Automation &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>KPIT Technologies</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=34953ee9e43bedae</t>
         </is>
